--- a/output/pdf_financials_xlsx/BYD.xlsx
+++ b/output/pdf_financials_xlsx/BYD.xlsx
@@ -1461,28 +1461,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>64.476</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>35.468</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>27.308</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>61.041</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>15.068</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>22.511</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>19.997</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1228.614</v>
       </c>
     </row>
     <row r="35">
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>64.476</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>35.468</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>27.308</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>61.041</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>15.068</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>22.511</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>19.997</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1228.614</v>
       </c>
     </row>
     <row r="37">
@@ -1895,28 +1895,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>97.83199999999999</v>
+        <v>33.356</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>70.223</v>
+        <v>34.755</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>51.513</v>
+        <v>24.205</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>26.359</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>57.254</v>
+        <v>42.186</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>71.95999999999999</v>
+        <v>49.449</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>76.967</v>
+        <v>56.97</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1292.599</v>
+        <v>63.985</v>
       </c>
     </row>
     <row r="49">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">

--- a/output/pdf_financials_xlsx/BYD.xlsx
+++ b/output/pdf_financials_xlsx/BYD.xlsx
@@ -1299,28 +1299,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>17.674</v>
+        <v>51.741</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>22.467</v>
+        <v>154.958</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>18.527</v>
+        <v>131.79</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>22.569</v>
+        <v>153.694</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>26.567</v>
+        <v>175.619</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>26.182</v>
+        <v>192.851</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26.309</v>
+        <v>225.319</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>28.02</v>
+        <v>243.972</v>
       </c>
     </row>
     <row r="29">
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>119.948</v>
+        <v>154.015</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>116.016</v>
+        <v>248.507</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>77.48</v>
+        <v>190.743</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>54.783</v>
+        <v>185.908</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>85.294</v>
+        <v>234.346</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>145.703</v>
+        <v>312.372</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>57.969</v>
+        <v>256.979</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>56.744</v>
+        <v>272.696</v>
       </c>
     </row>
     <row r="30">
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.432863012324809</v>
+        <v>8.259890926428165</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5.081011244566587</v>
+        <v>10.88355796918967</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.962772798778394</v>
+        <v>12.21752932314645</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.925395291215217</v>
+        <v>9.927429819455643</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.506696081680109</v>
+        <v>9.63467770250436</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.945811048789065</v>
+        <v>10.60330184644337</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.888030714493695</v>
+        <v>8.369719073640656</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.805527183773419</v>
+        <v>8.676865235201543</v>
       </c>
     </row>
     <row r="31">
@@ -3579,28 +3579,28 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>51.741</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>154.958</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>131.79</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>153.694</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>175.619</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>192.851</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>225.319</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>243.972</v>
       </c>
     </row>
     <row r="101">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10390,7 +10390,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -10444,7 +10448,11 @@
           <t>Depreciation of right of use assets 9</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -12266,7 +12274,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -12314,7 +12322,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>34.067</v>
       </c>
@@ -12360,7 +12372,11 @@
           <t>Depreciation of right of use assets 8</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -15758,7 +15774,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -15812,7 +15832,11 @@
           <t>Depreciation of right of use assets 9</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -15868,7 +15892,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -16888,7 +16912,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
         <v>34.067</v>
       </c>
@@ -16934,7 +16962,11 @@
           <t>Depreciation of right of use assets 8</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -16984,7 +17016,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">

--- a/output/pdf_financials_xlsx/BYD.xlsx
+++ b/output/pdf_financials_xlsx/BYD.xlsx
@@ -2162,25 +2162,25 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>379.432</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>425.96</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>559.001</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>579.532</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>759.336</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>914.345</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1050.849</v>
       </c>
     </row>
     <row r="57">
@@ -5994,7 +5994,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -7186,7 +7190,11 @@
           <t>Lease liabilities 15</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -8374,7 +8382,11 @@
           <t>Lease liabilities 15 450,423</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -9320,7 +9332,11 @@
           <t>Lease liabilities 4,14</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>4.561</v>
       </c>
